--- a/individual-projects/exercises/starwars-Exercise 1.xlsx
+++ b/individual-projects/exercises/starwars-Exercise 1.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micki\workspace\excel\individual-projects\exercises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9923E3-9372-4D7D-B858-1240C4A9318C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507CE0D4-601C-4B87-91A8-9133F18E3BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1830" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="750" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="starwars" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="SW Height" sheetId="3" r:id="rId2"/>
     <sheet name="data_dictionary" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1443,7 +1443,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1477,6 +1477,7 @@
     <xf numFmtId="0" fontId="20" fillId="5" borderId="4" xfId="9" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="4" xfId="11" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1841,24 +1842,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V88"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="9.25" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.625" style="3" customWidth="1"/>
-    <col min="7" max="8" width="12.75" customWidth="1"/>
-    <col min="9" max="9" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.09765625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="17.59765625" style="3" customWidth="1"/>
+    <col min="7" max="8" width="12.69921875" customWidth="1"/>
+    <col min="9" max="9" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.8984375" style="3" customWidth="1"/>
     <col min="14" max="14" width="11" style="3"/>
-    <col min="15" max="15" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.19921875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7" style="3" customWidth="1"/>
     <col min="20" max="20" width="13" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="36.75" customWidth="1"/>
-    <col min="22" max="22" width="125.25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="36.69921875" customWidth="1"/>
+    <col min="22" max="22" width="125.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1926,7 +1927,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2002,7 +2003,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -2070,7 +2071,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -2138,7 +2139,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -2206,7 +2207,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -2274,7 +2275,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -2342,7 +2343,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -2410,7 +2411,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -2478,7 +2479,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -2546,7 +2547,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -2614,7 +2615,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -2682,7 +2683,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -2750,7 +2751,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -2818,7 +2819,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -2886,7 +2887,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -2954,7 +2955,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -3022,7 +3023,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>73</v>
       </c>
@@ -3090,7 +3091,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>76</v>
       </c>
@@ -3158,7 +3159,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>78</v>
       </c>
@@ -3226,7 +3227,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>81</v>
       </c>
@@ -3294,7 +3295,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>85</v>
       </c>
@@ -3362,7 +3363,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>88</v>
       </c>
@@ -3430,7 +3431,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>91</v>
       </c>
@@ -3498,7 +3499,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>94</v>
       </c>
@@ -3566,7 +3567,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>98</v>
       </c>
@@ -3634,7 +3635,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>100</v>
       </c>
@@ -3702,7 +3703,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>105</v>
       </c>
@@ -3770,7 +3771,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>109</v>
       </c>
@@ -3836,7 +3837,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>110</v>
       </c>
@@ -3904,7 +3905,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>113</v>
       </c>
@@ -3972,7 +3973,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>116</v>
       </c>
@@ -4040,7 +4041,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>118</v>
       </c>
@@ -4108,7 +4109,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>122</v>
       </c>
@@ -4176,7 +4177,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>124</v>
       </c>
@@ -4244,7 +4245,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>127</v>
       </c>
@@ -4312,7 +4313,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>128</v>
       </c>
@@ -4380,7 +4381,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>129</v>
       </c>
@@ -4448,7 +4449,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>130</v>
       </c>
@@ -4516,7 +4517,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>135</v>
       </c>
@@ -4584,7 +4585,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -4652,7 +4653,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>140</v>
       </c>
@@ -4720,7 +4721,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -4788,7 +4789,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>144</v>
       </c>
@@ -4856,7 +4857,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>148</v>
       </c>
@@ -4924,7 +4925,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>150</v>
       </c>
@@ -4992,7 +4993,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>153</v>
       </c>
@@ -5060,7 +5061,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>156</v>
       </c>
@@ -5128,7 +5129,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>160</v>
       </c>
@@ -5196,7 +5197,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>162</v>
       </c>
@@ -5264,7 +5265,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>165</v>
       </c>
@@ -5332,7 +5333,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>168</v>
       </c>
@@ -5400,7 +5401,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>171</v>
       </c>
@@ -5468,7 +5469,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>173</v>
       </c>
@@ -5536,7 +5537,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>176</v>
       </c>
@@ -5604,7 +5605,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>179</v>
       </c>
@@ -5672,7 +5673,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>182</v>
       </c>
@@ -5740,7 +5741,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>185</v>
       </c>
@@ -5808,7 +5809,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>187</v>
       </c>
@@ -5876,7 +5877,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>188</v>
       </c>
@@ -5944,7 +5945,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>189</v>
       </c>
@@ -6012,7 +6013,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>193</v>
       </c>
@@ -6080,7 +6081,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>196</v>
       </c>
@@ -6148,7 +6149,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>197</v>
       </c>
@@ -6216,7 +6217,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>198</v>
       </c>
@@ -6284,7 +6285,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>200</v>
       </c>
@@ -6352,7 +6353,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>202</v>
       </c>
@@ -6420,7 +6421,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>204</v>
       </c>
@@ -6488,7 +6489,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>209</v>
       </c>
@@ -6556,7 +6557,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>212</v>
       </c>
@@ -6624,7 +6625,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>214</v>
       </c>
@@ -6692,7 +6693,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>215</v>
       </c>
@@ -6760,7 +6761,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>216</v>
       </c>
@@ -6828,7 +6829,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>220</v>
       </c>
@@ -6896,7 +6897,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>223</v>
       </c>
@@ -6964,7 +6965,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>227</v>
       </c>
@@ -7032,7 +7033,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>230</v>
       </c>
@@ -7100,7 +7101,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>234</v>
       </c>
@@ -7168,7 +7169,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>240</v>
       </c>
@@ -7236,7 +7237,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>241</v>
       </c>
@@ -7304,7 +7305,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>242</v>
       </c>
@@ -7372,7 +7373,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>244</v>
       </c>
@@ -7440,7 +7441,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>247</v>
       </c>
@@ -7506,7 +7507,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>249</v>
       </c>
@@ -7572,7 +7573,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>250</v>
       </c>
@@ -7638,7 +7639,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>251</v>
       </c>
@@ -7704,7 +7705,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>252</v>
       </c>
@@ -7770,7 +7771,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>253</v>
       </c>
@@ -7846,17 +7847,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE094AB-0F60-40D1-AD33-654FBC2EB7FA}">
   <dimension ref="A1:M94"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="9" style="3"/>
-    <col min="6" max="6" width="15.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.09765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.19921875" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -7885,7 +7886,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="str" cm="1">
         <f t="array" ref="A2:D82">_xlfn._xlws.FILTER(starwars!A2:D88,(ISNUMBER(starwars!B2:B88)) + (ISNUMBER(starwars!C2:C88)) + (ISNUMBER(starwars!D2:D88)))</f>
         <v>Luke Skywalker</v>
@@ -7919,12 +7920,12 @@
         <f>K2^2</f>
         <v>11741.461515012956</v>
       </c>
-      <c r="M2" s="14">
+      <c r="M2" s="17">
         <f>AVERAGE(L2:L82)</f>
         <v>1194.0570035055634</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <v>C-3PO</v>
       </c>
@@ -7954,12 +7955,12 @@
         <f t="shared" ref="L3:L66" si="1">K3^2</f>
         <v>9093.1528730376467</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="9">
         <f>_xlfn.VAR.P(L2:L82)</f>
         <v>5555621.222789621</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <v>R2-D2</v>
       </c>
@@ -7989,12 +7990,12 @@
         <f t="shared" si="1"/>
         <v>7457.7084285932024</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="9">
         <f>_xlfn.STDEV.P(L2:L82)</f>
         <v>2357.0365340379476</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <v>Darth Vader</v>
       </c>
@@ -8025,7 +8026,7 @@
         <v>6457.4121322969058</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <v>Leia Organa</v>
       </c>
@@ -8056,7 +8057,7 @@
         <v>6139.980033531474</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <v>Owen Lars</v>
       </c>
@@ -8087,7 +8088,7 @@
         <v>6139.980033531474</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <v>Beru Whitesun lars</v>
       </c>
@@ -8118,7 +8119,7 @@
         <v>5984.263984148758</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <v>R5-D4</v>
       </c>
@@ -8149,7 +8150,7 @@
         <v>3888.5232434080172</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <v>Biggs Darklighter</v>
       </c>
@@ -8180,7 +8181,7 @@
         <v>2741.3627495808569</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <v>Obi-Wan Kenobi</v>
       </c>
@@ -8211,7 +8212,7 @@
         <v>1395.622008840116</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <v>Anakin Skywalker</v>
       </c>
@@ -8242,7 +8243,7 @@
         <v>593.31336686480722</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <v>Wilhuff Tarkin</v>
       </c>
@@ -8273,7 +8274,7 @@
         <v>593.31336686480722</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <v>Chewbacca</v>
       </c>
@@ -8304,7 +8305,7 @@
         <v>301.30102118579487</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <v>Han Solo</v>
       </c>
@@ -8335,7 +8336,7 @@
         <v>206.15287303764671</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <v>Greedo</v>
       </c>
@@ -8366,7 +8367,7 @@
         <v>129.00472488949856</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <v>Jabba Desilijic Tiure</v>
       </c>
@@ -8397,7 +8398,7 @@
         <v>129.00472488949856</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <v>Wedge Antilles</v>
       </c>
@@ -8428,7 +8429,7 @@
         <v>87.57262612406646</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <v>Jek Tono Porkins</v>
       </c>
@@ -8459,7 +8460,7 @@
         <v>87.57262612406646</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <v>Yoda</v>
       </c>
@@ -8490,7 +8491,7 @@
         <v>87.57262612406646</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <v>Palpatine</v>
       </c>
@@ -8521,7 +8522,7 @@
         <v>69.856576741350409</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <v>Boba Fett</v>
       </c>
@@ -8552,7 +8553,7 @@
         <v>54.140527358634365</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <v>IG-88</v>
       </c>
@@ -8583,7 +8584,7 @@
         <v>54.140527358634365</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <v>Bossk</v>
       </c>
@@ -8614,7 +8615,7 @@
         <v>40.424477975918315</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <v>Lando Calrissian</v>
       </c>
@@ -8645,7 +8646,7 @@
         <v>18.992379210486213</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <v>Lobot</v>
       </c>
@@ -8676,7 +8677,7 @@
         <v>18.992379210486213</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <v>Ackbar</v>
       </c>
@@ -8707,7 +8708,7 @@
         <v>18.992379210486213</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <v>Mon Mothma</v>
       </c>
@@ -8738,7 +8739,7 @@
         <v>18.992379210486213</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <v>Wicket Systri Warrick</v>
       </c>
@@ -8769,7 +8770,7 @@
         <v>11.276329827770162</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <v>Nien Nunb</v>
       </c>
@@ -8800,7 +8801,7 @@
         <v>5.5602804450541106</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <v>Qui-Gon Jinn</v>
       </c>
@@ -8831,7 +8832,7 @@
         <v>1.8442310623380602</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <v>Nute Gunray</v>
       </c>
@@ -8862,7 +8863,7 @@
         <v>0.41213229690595854</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <v>Finis Valorum</v>
       </c>
@@ -8893,7 +8894,7 @@
         <v>0.41213229690595854</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <v>Jar Jar Binks</v>
       </c>
@@ -8924,7 +8925,7 @@
         <v>0.41213229690595854</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
         <v>Roos Tarpals</v>
       </c>
@@ -8955,7 +8956,7 @@
         <v>6.9800335314738566</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
         <v>Rugor Nass</v>
       </c>
@@ -8986,7 +8987,7 @@
         <v>13.263984148757807</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
         <v>Ric Olié</v>
       </c>
@@ -9017,7 +9018,7 @@
         <v>13.263984148757807</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
         <v>Watto</v>
       </c>
@@ -9048,7 +9049,7 @@
         <v>13.263984148757807</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="str">
         <v>Sebulba</v>
       </c>
@@ -9079,7 +9080,7 @@
         <v>13.263984148757807</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="str">
         <v>Quarsh Panaka</v>
       </c>
@@ -9110,7 +9111,7 @@
         <v>31.831885383325705</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="str">
         <v>Shmi Skywalker</v>
       </c>
@@ -9141,7 +9142,7 @@
         <v>31.831885383325705</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
         <v>Darth Maul</v>
       </c>
@@ -9172,7 +9173,7 @@
         <v>31.831885383325705</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="str">
         <v>Bib Fortuna</v>
       </c>
@@ -9203,7 +9204,7 @@
         <v>31.831885383325705</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="str">
         <v>Ayla Secura</v>
       </c>
@@ -9234,7 +9235,7 @@
         <v>31.831885383325705</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="str">
         <v>Dud Bolt</v>
       </c>
@@ -9265,7 +9266,7 @@
         <v>58.399786617893604</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
         <v>Gasgano</v>
       </c>
@@ -9296,7 +9297,7 @@
         <v>74.683737235177546</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="str">
         <v>Ben Quadinaros</v>
       </c>
@@ -9327,7 +9328,7 @@
         <v>74.683737235177546</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="str">
         <v>Mace Windu</v>
       </c>
@@ -9358,7 +9359,7 @@
         <v>74.683737235177546</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="str">
         <v>Ki-Adi-Mundi</v>
       </c>
@@ -9389,7 +9390,7 @@
         <v>74.683737235177546</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="str">
         <v>Kit Fisto</v>
       </c>
@@ -9420,7 +9421,7 @@
         <v>74.683737235177546</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="str">
         <v>Eeth Koth</v>
       </c>
@@ -9451,7 +9452,7 @@
         <v>74.683737235177546</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="str">
         <v>Adi Gallia</v>
       </c>
@@ -9482,7 +9483,7 @@
         <v>74.683737235177546</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="str">
         <v>Saesee Tiin</v>
       </c>
@@ -9513,7 +9514,7 @@
         <v>92.967687852461495</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="str">
         <v>Yarael Poof</v>
       </c>
@@ -9544,7 +9545,7 @@
         <v>113.25163846974544</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="str">
         <v>Plo Koon</v>
       </c>
@@ -9575,7 +9576,7 @@
         <v>186.10349032159729</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="str">
         <v>Mas Amedda</v>
       </c>
@@ -9606,7 +9607,7 @@
         <v>186.10349032159729</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="str">
         <v>Gregar Typho</v>
       </c>
@@ -9637,7 +9638,7 @@
         <v>186.10349032159729</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="str">
         <v>Cordé</v>
       </c>
@@ -9668,7 +9669,7 @@
         <v>186.10349032159729</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="str">
         <v>Cliegg Lars</v>
       </c>
@@ -9699,7 +9700,7 @@
         <v>186.10349032159729</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="str">
         <v>Poggle the Lesser</v>
       </c>
@@ -9730,7 +9731,7 @@
         <v>244.67139155616519</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="str">
         <v>Luminara Unduli</v>
       </c>
@@ -9761,7 +9762,7 @@
         <v>276.95534217344914</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="str">
         <v>Barriss Offee</v>
       </c>
@@ -9792,7 +9793,7 @@
         <v>276.95534217344914</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="str">
         <v>Dormé</v>
       </c>
@@ -9823,7 +9824,7 @@
         <v>276.95534217344914</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="str">
         <v>Dooku</v>
       </c>
@@ -9854,7 +9855,7 @@
         <v>347.52324340801704</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="str">
         <v>Bail Prestor Organa</v>
       </c>
@@ -9885,7 +9886,7 @@
         <v>347.52324340801704</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="str">
         <v>Jango Fett</v>
       </c>
@@ -9916,7 +9917,7 @@
         <v>347.52324340801704</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="str">
         <v>Zam Wesell</v>
       </c>
@@ -9947,7 +9948,7 @@
         <v>468.37509525986889</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="str">
         <v>Dexter Jettster</v>
       </c>
@@ -9978,7 +9979,7 @@
         <v>468.37509525986889</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="str">
         <v>Lama Su</v>
       </c>
@@ -10009,7 +10010,7 @@
         <v>468.37509525986889</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="str">
         <v>Taun We</v>
       </c>
@@ -10040,7 +10041,7 @@
         <v>558.94299649443678</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="str">
         <v>Jocasta Nu</v>
       </c>
@@ -10071,7 +10072,7 @@
         <v>558.94299649443678</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="str">
         <v>Ratts Tyerell</v>
       </c>
@@ -10102,7 +10103,7 @@
         <v>657.51089772900468</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="str">
         <v>R4-P17</v>
       </c>
@@ -10133,7 +10134,7 @@
         <v>764.07879896357258</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="str">
         <v>Wat Tambor</v>
       </c>
@@ -10164,7 +10165,7 @@
         <v>1001.2146014327084</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="str">
         <v>San Hill</v>
       </c>
@@ -10195,7 +10196,7 @@
         <v>1001.2146014327084</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="str">
         <v>Shaak Ti</v>
       </c>
@@ -10226,7 +10227,7 @@
         <v>1493.2022557536961</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="str">
         <v>Grievous</v>
       </c>
@@ -10257,7 +10258,7 @@
         <v>1734.0541076055479</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="str">
         <v>Tarfful</v>
       </c>
@@ -10288,7 +10289,7 @@
         <v>2464.3257125438195</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="str">
         <v>Raymus Antilles</v>
       </c>
@@ -10319,7 +10320,7 @@
         <v>2877.4615150129553</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="str">
         <v>Sly Moore</v>
       </c>
@@ -10350,7 +10351,7 @@
         <v>2985.7454656302393</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="str">
         <v>Tion Medon</v>
       </c>
@@ -10381,7 +10382,7 @@
         <v>3557.1652187166592</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="str">
         <v>Padmé Amidala</v>
       </c>
@@ -10412,7 +10413,7 @@
         <v>8035.6837372351774</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="10" t="s">
         <v>279</v>
       </c>
@@ -10442,7 +10443,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="10" t="s">
         <v>280</v>
       </c>
@@ -10468,7 +10469,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="15" t="s">
         <v>286</v>
       </c>
@@ -10498,7 +10499,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F87" s="16" t="s">
         <v>285</v>
       </c>
@@ -10509,7 +10510,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F88" s="11">
         <v>180</v>
       </c>
@@ -10520,7 +10521,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D90" s="5" t="s">
         <v>286</v>
       </c>
@@ -10537,7 +10538,7 @@
         <v>1.7435802469135797</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D91" s="5" t="s">
         <v>284</v>
       </c>
@@ -10554,7 +10555,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D92" s="5" t="s">
         <v>285</v>
       </c>
@@ -10571,7 +10572,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D93" s="3" t="s">
         <v>289</v>
       </c>
@@ -10580,23 +10581,23 @@
         <v>162</v>
       </c>
       <c r="F93">
-        <f t="shared" ref="F93:G93" si="10">ROUNDUP(SUM(F92*0.9), 0)</f>
+        <f>ROUNDUP(SUM(F92*0.9), 0)</f>
         <v>64</v>
       </c>
       <c r="G93">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="F93:G93" si="10">ROUNDUP(SUM(G92*0.9), 0)</f>
         <v>2</v>
       </c>
-      <c r="H93" s="3">
+      <c r="H93" s="5">
         <f>_xlfn.PERCENTILE.INC(F2:F82, 0.9)</f>
         <v>206</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D94" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94" s="5">
         <f>_xlfn.QUARTILE.INC(F2:F82,1)</f>
         <v>167</v>
       </c>
@@ -10612,13 +10613,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C9AD6C-192F-4898-AF47-D19C02D8C3A5}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10626,7 +10627,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -10634,7 +10635,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -10642,7 +10643,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -10650,7 +10651,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -10658,7 +10659,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -10666,7 +10667,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -10674,7 +10675,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -10682,7 +10683,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -10690,7 +10691,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
